--- a/data/trans_camb/IP17-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 12,14</t>
+          <t>-13,37; 12,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 15,62</t>
+          <t>-9,24; 15,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 4,06</t>
+          <t>-18,06; 3,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 18,12</t>
+          <t>-8,72; 18,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 16,57</t>
+          <t>-9,69; 16,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 5,97</t>
+          <t>-18,26; 4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 12,06</t>
+          <t>-6,55; 11,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 12,16</t>
+          <t>-5,33; 12,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 0,9</t>
+          <t>-15,99; 1,19</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 67,05</t>
+          <t>-44,6; 69,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 92,19</t>
+          <t>-31,61; 85,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 23,18</t>
+          <t>-61,93; 19,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 103,39</t>
+          <t>-28,68; 104,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 98,39</t>
+          <t>-31,72; 93,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,33; 40,83</t>
+          <t>-59,29; 32,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 59,14</t>
+          <t>-22,9; 56,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 61,69</t>
+          <t>-19,24; 60,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 4,97</t>
+          <t>-54,49; 7,34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 22,93</t>
+          <t>6,28; 24,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 22,87</t>
+          <t>6,2; 24,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,89</t>
+          <t>-9,63; 6,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 17,6</t>
+          <t>-0,52; 18,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 16,71</t>
+          <t>-0,49; 17,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 3,37</t>
+          <t>-12,36; 3,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 17,81</t>
+          <t>5,75; 18,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 17,72</t>
+          <t>5,55; 17,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 3,35</t>
+          <t>-8,26; 2,44</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,81; 277,47</t>
+          <t>40,84; 312,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 264,78</t>
+          <t>38,32; 285,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 76,77</t>
+          <t>-61,17; 66,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 130,54</t>
+          <t>-3,38; 136,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 122,32</t>
+          <t>-3,95; 139,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,87; 23,74</t>
+          <t>-57,39; 26,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 151,82</t>
+          <t>31,95; 152,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 143,26</t>
+          <t>30,57; 149,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 28,09</t>
+          <t>-48,63; 19,57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 18,22</t>
+          <t>-6,64; 19,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 0,71</t>
+          <t>-20,56; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 12,75</t>
+          <t>-10,97; 12,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 13,74</t>
+          <t>-9,75; 13,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,2; -2,48</t>
+          <t>-23,91; -2,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 9,66</t>
+          <t>-13,49; 11,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 12,58</t>
+          <t>-4,98; 12,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,61; -3,73</t>
+          <t>-20,37; -4,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 7,15</t>
+          <t>-10,12; 7,72</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 106,81</t>
+          <t>-23,13; 118,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 9,82</t>
+          <t>-71,28; 6,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 83,64</t>
+          <t>-38,38; 73,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 67,63</t>
+          <t>-30,8; 65,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,31; -8,58</t>
+          <t>-73,97; -12,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 48,79</t>
+          <t>-41,84; 57,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 62,51</t>
+          <t>-16,85; 61,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -14,44</t>
+          <t>-68,39; -20,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 34,04</t>
+          <t>-34,63; 36,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 10,35</t>
+          <t>-11,74; 11,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 16,12</t>
+          <t>-7,05; 16,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 6,58</t>
+          <t>-18,12; 5,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 7,52</t>
+          <t>-15,15; 6,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 18,17</t>
+          <t>-6,02; 17,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 9,56</t>
+          <t>-18,68; 8,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 5,44</t>
+          <t>-10,35; 4,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 14,24</t>
+          <t>-3,02; 13,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 1,79</t>
+          <t>-14,47; 2,5</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 53,65</t>
+          <t>-39,07; 60,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 81,73</t>
+          <t>-24,63; 82,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 38,18</t>
+          <t>-60,61; 27,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 38,36</t>
+          <t>-50,63; 35,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 92,69</t>
+          <t>-20,51; 90,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,53; 46,45</t>
+          <t>-65,18; 40,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 25,95</t>
+          <t>-35,94; 23,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 66,18</t>
+          <t>-10,7; 63,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 11,26</t>
+          <t>-52,62; 11,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 24,57</t>
+          <t>-5,29; 25,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 20,15</t>
+          <t>-8,18; 19,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 5,19</t>
+          <t>-18,86; 5,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 23,22</t>
+          <t>-4,28; 23,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 20,91</t>
+          <t>-4,56; 21,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 11,4</t>
+          <t>-12,69; 11,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 21,04</t>
+          <t>-0,54; 19,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 16,24</t>
+          <t>-2,81; 15,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 4,8</t>
+          <t>-11,42; 5,6</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 234,34</t>
+          <t>-27,53; 217,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 175,29</t>
+          <t>-36,65; 181,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,85; 56,44</t>
+          <t>-76,42; 71,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 281,44</t>
+          <t>-25,2; 298,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 257,09</t>
+          <t>-29,5; 257,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,7; 138,78</t>
+          <t>-63,94; 160,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 183,22</t>
+          <t>-3,7; 165,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 139,62</t>
+          <t>-15,01; 136,33</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,51; 47,18</t>
+          <t>-58,5; 49,91</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 20,77</t>
+          <t>-4,25; 22,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 14,83</t>
+          <t>-10,04; 15,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 11,22</t>
+          <t>-12,93; 10,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 20,88</t>
+          <t>-1,16; 22,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 14,55</t>
+          <t>-8,36; 13,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,65; 27,31</t>
+          <t>2,53; 28,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 17,78</t>
+          <t>-0,08; 18,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 10,19</t>
+          <t>-5,92; 10,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 16,84</t>
+          <t>-0,8; 16,42</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 145,09</t>
+          <t>-16,13; 164,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 106,76</t>
+          <t>-38,44; 121,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 86,0</t>
+          <t>-52,65; 79,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 188,48</t>
+          <t>-6,21; 214,16</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 130,36</t>
+          <t>-39,85; 130,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,52; 261,0</t>
+          <t>7,17; 268,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 123,69</t>
+          <t>-0,39; 129,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 71,23</t>
+          <t>-27,36; 77,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 115,57</t>
+          <t>-4,63; 116,65</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 5,32</t>
+          <t>-12,57; 4,75</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-25,54; -10,43</t>
+          <t>-25,26; -9,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 1,19</t>
+          <t>-16,9; 1,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 3,81</t>
+          <t>-13,09; 4,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -10,77</t>
+          <t>-25,88; -10,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -1,28</t>
+          <t>-18,75; -1,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 2,05</t>
+          <t>-10,37; 1,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-23,8; -13,0</t>
+          <t>-23,05; -12,7</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -2,2</t>
+          <t>-14,96; -2,05</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 26,31</t>
+          <t>-40,85; 22,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-81,26; -45,6</t>
+          <t>-81,96; -45,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,76; 6,05</t>
+          <t>-55,63; 8,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 15,78</t>
+          <t>-41,23; 18,33</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,87; -44,51</t>
+          <t>-78,88; -44,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,9; -4,92</t>
+          <t>-58,58; -6,68</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 8,49</t>
+          <t>-35,34; 5,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-78,49; -55,51</t>
+          <t>-77,37; -52,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-50,67; -8,94</t>
+          <t>-51,19; -8,84</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 7,0</t>
+          <t>-5,82; 6,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,47; 14,22</t>
+          <t>0,6; 13,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 0,69</t>
+          <t>-10,62; 1,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -1,98</t>
+          <t>-14,94; -2,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 3,55</t>
+          <t>-11,43; 3,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -2,47</t>
+          <t>-16,05; -2,56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 0,58</t>
+          <t>-8,56; 0,65</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,25</t>
+          <t>-3,6; 5,77</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -2,74</t>
+          <t>-11,17; -2,31</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 59,92</t>
+          <t>-34,07; 58,27</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3,18; 135,59</t>
+          <t>2,53; 123,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,78; 9,25</t>
+          <t>-62,16; 16,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-58,15; -10,63</t>
+          <t>-58,05; -8,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 19,98</t>
+          <t>-42,82; 20,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-62,75; -10,7</t>
+          <t>-62,6; -11,69</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 4,28</t>
+          <t>-42,2; 3,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 38,97</t>
+          <t>-17,49; 35,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-57,3; -17,5</t>
+          <t>-55,87; -14,36</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,06</t>
+          <t>-0,03; 6,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,06</t>
+          <t>-2,53; 4,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,61</t>
+          <t>-8,34; -0,61</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,79</t>
+          <t>-3,24; 3,78</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,63</t>
+          <t>-6,05; 0,76</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -1,81</t>
+          <t>-9,17; -2,06</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,32</t>
+          <t>-0,91; 4,15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,75</t>
+          <t>-3,54; 1,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,21</t>
+          <t>-7,31; -2,41</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 39,19</t>
+          <t>-0,15; 38,51</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 22,67</t>
+          <t>-12,08; 22,6</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,96; -3,16</t>
+          <t>-38,56; -3,14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 17,95</t>
+          <t>-13,33; 18,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 3,17</t>
+          <t>-24,95; 3,84</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -8,86</t>
+          <t>-36,66; -9,59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 22,06</t>
+          <t>-3,93; 21,08</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 8,35</t>
+          <t>-15,55; 7,63</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,84; -11,36</t>
+          <t>-33,09; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 12,17</t>
+          <t>-12,8; 13,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 15,25</t>
+          <t>-10,8; 15,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 3,3</t>
+          <t>-21,09; 4,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 18,91</t>
+          <t>-7,82; 18,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 16,28</t>
+          <t>-9,99; 16,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 4,91</t>
+          <t>-19,7; 3,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 11,33</t>
+          <t>-5,69; 13,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 12,0</t>
+          <t>-5,57; 13,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 1,19</t>
+          <t>-15,25; 1,88</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 69,74</t>
+          <t>-41,7; 70,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 85,79</t>
+          <t>-34,79; 87,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 19,84</t>
+          <t>-66,88; 25,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 104,02</t>
+          <t>-25,87; 99,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 93,11</t>
+          <t>-32,01; 97,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 32,69</t>
+          <t>-60,25; 21,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 56,5</t>
+          <t>-19,92; 67,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 60,06</t>
+          <t>-18,39; 72,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 7,34</t>
+          <t>-52,86; 9,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 24,01</t>
+          <t>5,62; 22,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 24,43</t>
+          <t>7,26; 23,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 6,43</t>
+          <t>-10,52; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 18,14</t>
+          <t>0,28; 17,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 17,94</t>
+          <t>-0,4; 16,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 3,45</t>
+          <t>-12,55; 2,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 18,0</t>
+          <t>5,65; 18,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 17,88</t>
+          <t>5,51; 17,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 2,44</t>
+          <t>-8,67; 2,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 312,94</t>
+          <t>34,15; 281,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,32; 285,31</t>
+          <t>44,74; 293,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 66,2</t>
+          <t>-65,42; 70,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 136,96</t>
+          <t>0,23; 131,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 139,25</t>
+          <t>-2,04; 127,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,39; 26,43</t>
+          <t>-59,06; 24,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,95; 152,01</t>
+          <t>27,99; 147,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 149,27</t>
+          <t>31,1; 139,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,63; 19,57</t>
+          <t>-49,73; 19,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 19,41</t>
+          <t>-6,04; 18,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 0,89</t>
+          <t>-20,63; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 12,62</t>
+          <t>-11,57; 12,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 13,84</t>
+          <t>-9,67; 15,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -2,88</t>
+          <t>-24,1; -3,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 11,14</t>
+          <t>-14,4; 9,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 12,44</t>
+          <t>-4,52; 12,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,37; -4,96</t>
+          <t>-19,66; -4,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 7,72</t>
+          <t>-9,15; 7,99</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 118,62</t>
+          <t>-20,68; 117,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 6,43</t>
+          <t>-72,02; 10,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 73,29</t>
+          <t>-39,38; 77,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 65,61</t>
+          <t>-29,14; 76,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,97; -12,48</t>
+          <t>-75,24; -12,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 57,73</t>
+          <t>-45,09; 46,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 61,8</t>
+          <t>-16,26; 62,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,39; -20,73</t>
+          <t>-66,92; -19,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 36,95</t>
+          <t>-31,48; 40,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 11,73</t>
+          <t>-12,79; 10,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 16,4</t>
+          <t>-6,81; 17,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 5,35</t>
+          <t>-17,71; 6,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 6,41</t>
+          <t>-15,27; 5,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 17,57</t>
+          <t>-7,48; 17,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 8,64</t>
+          <t>-20,92; 7,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 4,88</t>
+          <t>-10,75; 4,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 13,24</t>
+          <t>-3,07; 13,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 2,5</t>
+          <t>-15,36; 2,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 60,83</t>
+          <t>-41,67; 55,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 82,73</t>
+          <t>-21,24; 94,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 27,09</t>
+          <t>-58,53; 31,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,63; 35,4</t>
+          <t>-49,85; 33,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 90,42</t>
+          <t>-22,55; 88,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 40,37</t>
+          <t>-67,57; 37,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 23,01</t>
+          <t>-36,05; 21,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 63,1</t>
+          <t>-10,37; 68,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 11,68</t>
+          <t>-53,3; 15,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 25,44</t>
+          <t>-6,02; 23,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 19,99</t>
+          <t>-9,63; 19,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 5,93</t>
+          <t>-19,88; 5,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 23,79</t>
+          <t>-2,66; 23,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 21,56</t>
+          <t>-4,97; 20,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 11,23</t>
+          <t>-13,05; 10,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 19,57</t>
+          <t>-0,17; 20,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 15,95</t>
+          <t>-2,82; 16,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 5,6</t>
+          <t>-12,01; 5,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 217,34</t>
+          <t>-25,81; 197,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 181,9</t>
+          <t>-38,81; 169,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,42; 71,38</t>
+          <t>-77,57; 61,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 298,04</t>
+          <t>-17,62; 272,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 257,86</t>
+          <t>-25,25; 256,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 160,94</t>
+          <t>-65,83; 153,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 165,58</t>
+          <t>-2,32; 167,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 136,33</t>
+          <t>-14,3; 143,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 49,91</t>
+          <t>-61,56; 51,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 22,94</t>
+          <t>-5,84; 21,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 15,2</t>
+          <t>-12,65; 13,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 10,83</t>
+          <t>-13,55; 12,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 22,1</t>
+          <t>-1,56; 21,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 13,94</t>
+          <t>-8,51; 15,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53; 28,54</t>
+          <t>2,53; 26,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 18,06</t>
+          <t>0,84; 18,34</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 10,69</t>
+          <t>-5,94; 10,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 16,42</t>
+          <t>-1,7; 16,43</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 164,67</t>
+          <t>-22,25; 141,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 121,81</t>
+          <t>-47,08; 91,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 79,65</t>
+          <t>-51,79; 81,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 214,16</t>
+          <t>-9,77; 190,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 130,1</t>
+          <t>-42,79; 146,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,17; 268,58</t>
+          <t>11,29; 276,93</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 129,56</t>
+          <t>3,28; 129,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 77,48</t>
+          <t>-27,8; 73,33</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 116,65</t>
+          <t>-8,66; 116,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 4,75</t>
+          <t>-12,39; 4,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-25,26; -9,92</t>
+          <t>-24,88; -10,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 1,22</t>
+          <t>-16,51; 1,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 4,37</t>
+          <t>-12,69; 4,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-25,88; -10,97</t>
+          <t>-25,77; -11,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -1,79</t>
+          <t>-18,02; -0,98</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 1,6</t>
+          <t>-9,97; 2,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-23,05; -12,7</t>
+          <t>-22,84; -12,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -2,05</t>
+          <t>-15,31; -2,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 22,91</t>
+          <t>-41,17; 20,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-81,96; -45,04</t>
+          <t>-82,46; -47,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 8,95</t>
+          <t>-54,25; 11,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 18,33</t>
+          <t>-39,85; 18,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,88; -44,84</t>
+          <t>-79,79; -47,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-58,58; -6,68</t>
+          <t>-57,51; -3,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 5,94</t>
+          <t>-33,54; 9,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,37; -52,12</t>
+          <t>-77,04; -53,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-51,19; -8,84</t>
+          <t>-50,37; -10,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 6,39</t>
+          <t>-5,3; 6,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,6; 13,5</t>
+          <t>0,44; 13,9</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 1,44</t>
+          <t>-10,22; 0,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,94; -2,01</t>
+          <t>-14,9; -1,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 3,51</t>
+          <t>-10,44; 3,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -2,56</t>
+          <t>-15,48; -2,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 0,65</t>
+          <t>-8,63; 0,63</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,77</t>
+          <t>-3,28; 6,44</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -2,31</t>
+          <t>-11,39; -2,55</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 58,27</t>
+          <t>-29,99; 62,64</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2,53; 123,16</t>
+          <t>1,78; 124,34</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 16,21</t>
+          <t>-62,08; 9,15</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-58,05; -8,84</t>
+          <t>-57,44; -7,71</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 20,05</t>
+          <t>-41,17; 19,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-62,6; -11,69</t>
+          <t>-61,63; -12,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 3,43</t>
+          <t>-42,15; 5,04</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 35,76</t>
+          <t>-15,56; 41,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -14,36</t>
+          <t>-55,52; -14,9</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,95</t>
+          <t>-0,0; 7,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,08</t>
+          <t>-2,5; 4,47</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -0,61</t>
+          <t>-8,27; -0,93</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,78</t>
+          <t>-3,49; 3,86</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,76</t>
+          <t>-6,22; 0,84</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -2,06</t>
+          <t>-8,53; -1,93</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,15</t>
+          <t>-0,67; 4,35</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,51</t>
+          <t>-3,37; 1,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -2,41</t>
+          <t>-7,19; -2,22</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 38,51</t>
+          <t>0,04; 39,78</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 22,6</t>
+          <t>-11,5; 24,5</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-38,56; -3,14</t>
+          <t>-38,79; -5,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 18,15</t>
+          <t>-14,77; 18,8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 3,84</t>
+          <t>-26,01; 4,05</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,66; -9,59</t>
+          <t>-36,05; -8,98</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 21,08</t>
+          <t>-3,01; 22,02</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 7,63</t>
+          <t>-15,05; 7,14</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-33,09; -12,02</t>
+          <t>-32,64; -11,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,76</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,8</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,24</t>
+          <t>-5,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 13,03</t>
+          <t>-9,02; 18,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 15,22</t>
+          <t>-11,28; 16,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 4,06</t>
+          <t>-17,95; 7,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 18,14</t>
+          <t>-12,54; 12,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 16,06</t>
+          <t>-12,3; 15,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 3,49</t>
+          <t>-16,89; 8,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 13,85</t>
+          <t>-6,7; 12,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 13,64</t>
+          <t>-6,55; 12,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 1,88</t>
+          <t>-13,99; 3,55</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-22,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-0,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,39%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-31,87%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-27,73%</t>
+          <t>-18,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-29,72%</t>
+          <t>-20,79%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 70,42</t>
+          <t>-27,46; 103,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 87,62</t>
+          <t>-36,9; 98,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 25,12</t>
+          <t>-56,8; 46,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 99,42</t>
+          <t>-42,41; 67,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 97,39</t>
+          <t>-39,73; 92,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 21,16</t>
+          <t>-54,71; 47,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 67,43</t>
+          <t>-23,64; 59,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 72,58</t>
+          <t>-22,64; 61,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,86; 9,27</t>
+          <t>-48,25; 18,02</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>14,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>15,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,19</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-2,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 22,64</t>
+          <t>-1,37; 17,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 23,94</t>
+          <t>-1,16; 16,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 6,55</t>
+          <t>-12,69; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 17,64</t>
+          <t>5,82; 22,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 16,93</t>
+          <t>4,74; 22,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 2,94</t>
+          <t>-6,54; 8,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,0</t>
+          <t>5,27; 17,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 17,18</t>
+          <t>5,2; 17,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 2,68</t>
+          <t>-7,13; 4,02</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-29,59%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>120,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>128,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-9,87%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>46,32%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,61%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,97%</t>
+          <t>-14,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,15; 281,95</t>
+          <t>-5,11; 130,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,74; 293,16</t>
+          <t>-5,42; 122,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,42; 70,66</t>
+          <t>-58,68; 22,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 131,34</t>
+          <t>34,81; 277,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 127,8</t>
+          <t>30,7; 264,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 24,9</t>
+          <t>-42,15; 111,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,99; 147,45</t>
+          <t>29,32; 151,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,1; 139,5</t>
+          <t>28,94; 143,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 19,34</t>
+          <t>-41,08; 34,62</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,49</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,01</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,72</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-13,49</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-1,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 18,77</t>
+          <t>-9,21; 13,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 1,49</t>
+          <t>-23,2; -2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 12,99</t>
+          <t>-14,98; 8,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 15,16</t>
+          <t>-6,68; 18,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,1; -3,42</t>
+          <t>-21,48; 0,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 9,36</t>
+          <t>-10,62; 12,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 12,89</t>
+          <t>-4,79; 12,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -4,16</t>
+          <t>-19,61; -3,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 7,99</t>
+          <t>-9,59; 6,95</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-50,58%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-11,3%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>27,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-42,28%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-50,58%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,29%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,56%</t>
+          <t>-4,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 117,12</t>
+          <t>-30,24; 67,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,02; 10,2</t>
+          <t>-72,31; -8,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 77,22</t>
+          <t>-48,17; 39,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 76,61</t>
+          <t>-23,52; 106,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,24; -12,8</t>
+          <t>-72,73; 9,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 46,2</t>
+          <t>-36,64; 85,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 62,22</t>
+          <t>-17,72; 62,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,92; -19,56</t>
+          <t>-65,69; -14,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 40,77</t>
+          <t>-32,27; 34,6</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,95</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,16</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>-6,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,14</t>
+          <t>-6,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 10,84</t>
+          <t>-14,12; 7,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 17,23</t>
+          <t>-5,37; 18,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 6,18</t>
+          <t>-17,37; 10,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 5,85</t>
+          <t>-13,22; 10,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 17,7</t>
+          <t>-6,63; 16,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 7,12</t>
+          <t>-17,89; 6,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 4,58</t>
+          <t>-10,34; 5,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 13,91</t>
+          <t>-2,8; 14,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 2,68</t>
+          <t>-14,57; 1,99</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-16,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-21,95%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-2,07%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>19,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-25,13%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-16,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,98%</t>
+          <t>-26,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-24,55%</t>
+          <t>-24,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 55,84</t>
+          <t>-46,33; 38,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 94,23</t>
+          <t>-17,92; 92,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 31,37</t>
+          <t>-61,2; 48,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 33,94</t>
+          <t>-42,22; 53,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 88,15</t>
+          <t>-22,62; 81,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 37,19</t>
+          <t>-59,5; 40,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 21,66</t>
+          <t>-36,63; 25,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 68,43</t>
+          <t>-9,12; 66,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,3; 15,23</t>
+          <t>-49,87; 10,84</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,69</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,28</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>9,84</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,87</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-6,41</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,69</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,28</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 23,73</t>
+          <t>-3,24; 23,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 19,01</t>
+          <t>-5,77; 20,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 5,89</t>
+          <t>-13,88; 11,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 23,28</t>
+          <t>-5,62; 24,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 20,87</t>
+          <t>-8,28; 20,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 10,62</t>
+          <t>-18,21; 6,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 20,35</t>
+          <t>0,25; 21,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 16,51</t>
+          <t>-3,55; 16,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 5,31</t>
+          <t>-11,44; 5,29</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-2,75%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>54,95%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>32,79%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-35,81%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,67%</t>
+          <t>-33,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-21,85%</t>
+          <t>-19,46%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 197,7</t>
+          <t>-20,08; 281,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 169,77</t>
+          <t>-30,1; 257,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,57; 61,96</t>
+          <t>-67,85; 141,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 272,04</t>
+          <t>-23,99; 234,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 256,2</t>
+          <t>-39,01; 175,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 153,65</t>
+          <t>-76,91; 61,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 167,64</t>
+          <t>-3,88; 183,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 143,73</t>
+          <t>-19,56; 139,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 51,71</t>
+          <t>-57,63; 49,73</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>10,01</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13,67</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>8,25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,36</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10,01</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>6,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 21,01</t>
+          <t>-3,17; 20,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 13,5</t>
+          <t>-9,06; 14,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 12,08</t>
+          <t>1,97; 26,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 21,7</t>
+          <t>-6,02; 20,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 15,48</t>
+          <t>-11,03; 14,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53; 26,67</t>
+          <t>-13,23; 10,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 18,34</t>
+          <t>-0,35; 17,78</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 10,73</t>
+          <t>-6,3; 10,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 16,43</t>
+          <t>-1,88; 16,13</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>62,85%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>85,78%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>39,85%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-4,45%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>-4,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 141,16</t>
+          <t>-14,13; 188,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 91,73</t>
+          <t>-42,88; 130,36</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,79; 81,09</t>
+          <t>5,95; 249,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 190,5</t>
+          <t>-24,52; 145,09</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 146,66</t>
+          <t>-40,65; 106,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,29; 276,93</t>
+          <t>-52,37; 87,78</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,28; 129,93</t>
+          <t>-1,74; 123,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 73,33</t>
+          <t>-29,72; 71,23</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 116,37</t>
+          <t>-9,46; 111,06</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-4,61</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-18,29</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-7,97</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-3,86</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-17,58</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-7,8</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-4,61</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-18,29</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-9,9</t>
+          <t>-9,51</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-8,88</t>
+          <t>-8,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 4,66</t>
+          <t>-13,53; 3,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,88; -10,42</t>
+          <t>-26,34; -10,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 1,96</t>
+          <t>-16,41; 0,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 4,09</t>
+          <t>-11,89; 5,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-25,77; -11,11</t>
+          <t>-25,54; -10,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,02; -0,98</t>
+          <t>-17,59; -1,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 2,28</t>
+          <t>-10,68; 2,05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -12,73</t>
+          <t>-23,8; -13,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -2,31</t>
+          <t>-14,58; -2,76</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-16,67%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-66,09%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-28,8%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-15,02%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-68,41%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-30,34%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-16,67%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-66,09%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-35,78%</t>
+          <t>-36,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-33,25%</t>
+          <t>-32,34%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 20,6</t>
+          <t>-41,22; 15,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-82,46; -47,47</t>
+          <t>-78,87; -44,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 11,24</t>
+          <t>-52,11; 2,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 18,06</t>
+          <t>-38,68; 26,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,79; -47,48</t>
+          <t>-81,26; -45,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,51; -3,62</t>
+          <t>-58,64; -7,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 9,92</t>
+          <t>-36,28; 8,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,04; -53,84</t>
+          <t>-78,49; -55,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-50,37; -10,05</t>
+          <t>-49,08; -10,92</t>
         </is>
       </c>
     </row>
@@ -2136,39 +2136,39 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-8,26</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-3,84</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-9,88</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,74</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>7,19</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-4,92</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-8,26</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-5,92</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-3,84</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-9,35</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-3,84</t>
-        </is>
-      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>1,56</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-7,06</t>
+          <t>-7,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,73</t>
+          <t>-15,04; -1,98</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,44; 13,9</t>
+          <t>-11,04; 3,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 0,88</t>
+          <t>-16,77; -3,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,9; -1,62</t>
+          <t>-5,48; 7,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 3,19</t>
+          <t>0,47; 14,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -2,82</t>
+          <t>-11,62; -0,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 0,63</t>
+          <t>-8,29; 0,58</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 6,44</t>
+          <t>-3,41; 6,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -2,55</t>
+          <t>-12,09; -3,52</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-37,4%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-17,42%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-44,75%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>51,26%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-35,11%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-37,4%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-17,42%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-42,38%</t>
+          <t>-42,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-38,94%</t>
+          <t>-43,29%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 62,64</t>
+          <t>-58,15; -10,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1,78; 124,34</t>
+          <t>-42,24; 19,98</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 9,15</t>
+          <t>-64,93; -13,29</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-57,44; -7,71</t>
+          <t>-33,59; 59,92</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 19,05</t>
+          <t>3,18; 135,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-61,63; -12,18</t>
+          <t>-67,38; -0,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 5,04</t>
+          <t>-39,62; 4,28</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 41,1</t>
+          <t>-16,94; 38,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-55,52; -14,9</t>
+          <t>-60,28; -22,44</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-5,03</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>3,36</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>-4,43</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-4,71</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 7,06</t>
+          <t>-3,38; 3,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,47</t>
+          <t>-6,38; 0,63</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,93</t>
+          <t>-8,71; -1,6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,86</t>
+          <t>-0,3; 7,06</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,84</t>
+          <t>-2,89; 4,06</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -1,93</t>
+          <t>-7,68; -0,88</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,35</t>
+          <t>-0,73; 4,32</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,41</t>
+          <t>-3,47; 1,75</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -2,22</t>
+          <t>-7,07; -2,23</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-11,92%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-22,44%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>17,15%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-23,14%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-11,92%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-22,88%</t>
+          <t>-22,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-22,8%</t>
+          <t>-22,37%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,04; 39,78</t>
+          <t>-13,77; 17,95</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 24,5</t>
+          <t>-26,02; 3,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-38,79; -5,31</t>
+          <t>-35,76; -7,77</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 18,8</t>
+          <t>-1,36; 39,19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 4,05</t>
+          <t>-13,2; 22,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,05; -8,98</t>
+          <t>-35,76; -4,43</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 22,02</t>
+          <t>-3,07; 22,06</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 7,14</t>
+          <t>-15,78; 8,35</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,64; -11,15</t>
+          <t>-32,1; -11,21</t>
         </is>
       </c>
     </row>
